--- a/erp-server/erp-server-bi/src/main/resources/excel/biNewAndOldSalesExport.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biNewAndOldSalesExport.xlsx
@@ -98,12 +98,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -741,13 +740,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,43 +1081,43 @@
     <col min="8" max="8" width="14.5" customWidth="1"/>
     <col min="9" max="9" width="16.25" customWidth="1"/>
     <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="12.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="12.75" customWidth="1"/>
     <col min="13" max="13" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -1129,43 +1128,43 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
